--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/146.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/146.xlsx
@@ -426,13 +426,13 @@
         <v>-10.3111760173018</v>
       </c>
       <c r="E2">
-        <v>-15.36779071287166</v>
+        <v>-12.66776506985634</v>
       </c>
       <c r="F2">
-        <v>-6.159543831390168</v>
+        <v>-5.976528479252659</v>
       </c>
       <c r="G2">
-        <v>-13.91438641305689</v>
+        <v>-11.35636577264315</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.28527054890079</v>
       </c>
       <c r="E3">
-        <v>-16.12155521144839</v>
+        <v>-12.32648568321628</v>
       </c>
       <c r="F3">
-        <v>-6.242327556156339</v>
+        <v>-5.611954044871763</v>
       </c>
       <c r="G3">
-        <v>-13.72485649334025</v>
+        <v>-11.33766280975431</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.28883239965852</v>
       </c>
       <c r="E4">
-        <v>-16.3742440610764</v>
+        <v>-13.72454787818232</v>
       </c>
       <c r="F4">
-        <v>-5.751190179771318</v>
+        <v>-6.095011525609878</v>
       </c>
       <c r="G4">
-        <v>-13.79108630990686</v>
+        <v>-10.89964926256248</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.31542757884328</v>
       </c>
       <c r="E5">
-        <v>-17.11386160685316</v>
+        <v>-14.16644995727282</v>
       </c>
       <c r="F5">
-        <v>-5.883272533780296</v>
+        <v>-6.297370084970158</v>
       </c>
       <c r="G5">
-        <v>-14.14683963260341</v>
+        <v>-10.99944105384987</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.33152026575316</v>
       </c>
       <c r="E6">
-        <v>-18.14008627257539</v>
+        <v>-14.20795342155312</v>
       </c>
       <c r="F6">
-        <v>-5.807146397830425</v>
+        <v>-6.58781806231154</v>
       </c>
       <c r="G6">
-        <v>-14.53483587895385</v>
+        <v>-11.39086453611915</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.31561936516698</v>
       </c>
       <c r="E7">
-        <v>-18.7376818165236</v>
+        <v>-14.11650541744222</v>
       </c>
       <c r="F7">
-        <v>-5.728580719879308</v>
+        <v>-6.341384972734208</v>
       </c>
       <c r="G7">
-        <v>-14.32159093041632</v>
+        <v>-10.46217711692795</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.24752427929576</v>
       </c>
       <c r="E8">
-        <v>-19.03601768414892</v>
+        <v>-13.89257690623693</v>
       </c>
       <c r="F8">
-        <v>-5.535745072181611</v>
+        <v>-6.103812929264623</v>
       </c>
       <c r="G8">
-        <v>-13.66655574867203</v>
+        <v>-11.08264955137583</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.10495317750358</v>
       </c>
       <c r="E9">
-        <v>-18.94140880518068</v>
+        <v>-16.07674143266848</v>
       </c>
       <c r="F9">
-        <v>-5.692361183559303</v>
+        <v>-5.834576956006727</v>
       </c>
       <c r="G9">
-        <v>-13.73957277203436</v>
+        <v>-9.946841583687803</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.884927911737201</v>
       </c>
       <c r="E10">
-        <v>-19.39299276169957</v>
+        <v>-16.58073341887815</v>
       </c>
       <c r="F10">
-        <v>-5.611104139916491</v>
+        <v>-5.618482408373226</v>
       </c>
       <c r="G10">
-        <v>-13.62441173896252</v>
+        <v>-10.41293910620692</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.578628817114293</v>
       </c>
       <c r="E11">
-        <v>-20.86409018546133</v>
+        <v>-15.94984453402554</v>
       </c>
       <c r="F11">
-        <v>-5.820667010578918</v>
+        <v>-5.819358190082495</v>
       </c>
       <c r="G11">
-        <v>-13.02981501773243</v>
+        <v>-10.67310388243374</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.207927185904611</v>
       </c>
       <c r="E12">
-        <v>-21.6792834339521</v>
+        <v>-18.75370355756274</v>
       </c>
       <c r="F12">
-        <v>-5.644581780133231</v>
+        <v>-5.979889994173219</v>
       </c>
       <c r="G12">
-        <v>-12.89259761333801</v>
+        <v>-10.13561026000266</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.791475393476638</v>
       </c>
       <c r="E13">
-        <v>-21.58711540247399</v>
+        <v>-19.62321132330151</v>
       </c>
       <c r="F13">
-        <v>-5.663928300825613</v>
+        <v>-5.765161424386934</v>
       </c>
       <c r="G13">
-        <v>-12.45092550410739</v>
+        <v>-9.203779430557512</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.373470820659204</v>
       </c>
       <c r="E14">
-        <v>-23.14780415600349</v>
+        <v>-20.34041745121432</v>
       </c>
       <c r="F14">
-        <v>-5.139208909931099</v>
+        <v>-5.553781115642765</v>
       </c>
       <c r="G14">
-        <v>-12.51464682679181</v>
+        <v>-7.775791807887171</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.9944583839723</v>
       </c>
       <c r="E15">
-        <v>-23.31216512011189</v>
+        <v>-21.25894594808613</v>
       </c>
       <c r="F15">
-        <v>-5.170908873701431</v>
+        <v>-5.432071578251642</v>
       </c>
       <c r="G15">
-        <v>-11.94755002345142</v>
+        <v>-8.026260574405825</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.688156452592611</v>
       </c>
       <c r="E16">
-        <v>-23.32690530300686</v>
+        <v>-20.85050929191232</v>
       </c>
       <c r="F16">
-        <v>-5.016009967949743</v>
+        <v>-5.109069590347642</v>
       </c>
       <c r="G16">
-        <v>-11.68605307127147</v>
+        <v>-7.149879108093735</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.485712927218183</v>
       </c>
       <c r="E17">
-        <v>-23.8340717494959</v>
+        <v>-22.34947494471728</v>
       </c>
       <c r="F17">
-        <v>-4.914725485609448</v>
+        <v>-4.44614869543967</v>
       </c>
       <c r="G17">
-        <v>-11.23262434519337</v>
+        <v>-8.440734638130202</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.38718063499903</v>
       </c>
       <c r="E18">
-        <v>-25.01889263191476</v>
+        <v>-23.27068882667563</v>
       </c>
       <c r="F18">
-        <v>-4.60248316190041</v>
+        <v>-4.22547990300791</v>
       </c>
       <c r="G18">
-        <v>-10.4790261896357</v>
+        <v>-7.171095486697104</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.394901307189075</v>
       </c>
       <c r="E19">
-        <v>-25.72324695059379</v>
+        <v>-22.14642269868735</v>
       </c>
       <c r="F19">
-        <v>-4.274430617941541</v>
+        <v>-4.364456758910389</v>
       </c>
       <c r="G19">
-        <v>-10.86363457472601</v>
+        <v>-8.614317821067946</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.48092524854473</v>
       </c>
       <c r="E20">
-        <v>-26.43422189827205</v>
+        <v>-23.05718939111001</v>
       </c>
       <c r="F20">
-        <v>-4.116200018495794</v>
+        <v>-4.204603387722557</v>
       </c>
       <c r="G20">
-        <v>-10.31474198859742</v>
+        <v>-8.462026484829439</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.625632654845407</v>
       </c>
       <c r="E21">
-        <v>-26.58377928084937</v>
+        <v>-24.07826518188551</v>
       </c>
       <c r="F21">
-        <v>-3.984338838583363</v>
+        <v>-3.895146035221732</v>
       </c>
       <c r="G21">
-        <v>-10.28019728801959</v>
+        <v>-7.218203984626053</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.793450895307631</v>
       </c>
       <c r="E22">
-        <v>-27.88030856008944</v>
+        <v>-25.50337142362537</v>
       </c>
       <c r="F22">
-        <v>-3.939645103732718</v>
+        <v>-3.447710837906204</v>
       </c>
       <c r="G22">
-        <v>-11.06587594676395</v>
+        <v>-7.705288200239383</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.953788388555865</v>
       </c>
       <c r="E23">
-        <v>-27.81789713131572</v>
+        <v>-25.05061459233848</v>
       </c>
       <c r="F23">
-        <v>-3.811492524682621</v>
+        <v>-3.563660736745662</v>
       </c>
       <c r="G23">
-        <v>-9.999170505117826</v>
+        <v>-8.401888256087936</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.081284867696155</v>
       </c>
       <c r="E24">
-        <v>-28.83031447978857</v>
+        <v>-25.18602955058985</v>
       </c>
       <c r="F24">
-        <v>-3.629537482820695</v>
+        <v>-2.919101433688144</v>
       </c>
       <c r="G24">
-        <v>-10.69419557461785</v>
+        <v>-8.021430616270321</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.148014552767066</v>
       </c>
       <c r="E25">
-        <v>-29.04290369207865</v>
+        <v>-26.886430784204</v>
       </c>
       <c r="F25">
-        <v>-3.603877974151578</v>
+        <v>-3.185341202050114</v>
       </c>
       <c r="G25">
-        <v>-10.28401006747166</v>
+        <v>-8.735253804084401</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.145340475293276</v>
       </c>
       <c r="E26">
-        <v>-28.28158117038312</v>
+        <v>-25.08786581952558</v>
       </c>
       <c r="F26">
-        <v>-3.484134980974701</v>
+        <v>-3.347019466626313</v>
       </c>
       <c r="G26">
-        <v>-10.94131421392431</v>
+        <v>-8.422038237684486</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.05950372305465</v>
       </c>
       <c r="E27">
-        <v>-28.80714680676532</v>
+        <v>-26.61587710461574</v>
       </c>
       <c r="F27">
-        <v>-3.333799551245036</v>
+        <v>-3.185542495328994</v>
       </c>
       <c r="G27">
-        <v>-9.828320579739099</v>
+        <v>-8.755567846758924</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.898326916340717</v>
       </c>
       <c r="E28">
-        <v>-28.90396558104932</v>
+        <v>-25.7185871508399</v>
       </c>
       <c r="F28">
-        <v>-3.228583637211054</v>
+        <v>-3.593414037119415</v>
       </c>
       <c r="G28">
-        <v>-10.51811866329492</v>
+        <v>-7.967690769569736</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.665677815286252</v>
       </c>
       <c r="E29">
-        <v>-27.99011046935342</v>
+        <v>-25.70625158764301</v>
       </c>
       <c r="F29">
-        <v>-3.646076666384991</v>
+        <v>-3.226969149142997</v>
       </c>
       <c r="G29">
-        <v>-10.77797500469515</v>
+        <v>-7.919732435256892</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.379387292689004</v>
       </c>
       <c r="E30">
-        <v>-27.72430263052519</v>
+        <v>-26.27125570415802</v>
       </c>
       <c r="F30">
-        <v>-3.447626344431118</v>
+        <v>-3.111833535460491</v>
       </c>
       <c r="G30">
-        <v>-10.4236129199398</v>
+        <v>-8.265097410496246</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.058580206742738</v>
       </c>
       <c r="E31">
-        <v>-28.51122008731208</v>
+        <v>-23.60886620862044</v>
       </c>
       <c r="F31">
-        <v>-3.654161532236313</v>
+        <v>-3.435487448510495</v>
       </c>
       <c r="G31">
-        <v>-10.82475866168971</v>
+        <v>-7.895973109944952</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.720551344216823</v>
       </c>
       <c r="E32">
-        <v>-27.63659514594464</v>
+        <v>-25.63432583497918</v>
       </c>
       <c r="F32">
-        <v>-3.559690371784044</v>
+        <v>-3.236327215692424</v>
       </c>
       <c r="G32">
-        <v>-10.81950214475148</v>
+        <v>-8.205385740557471</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.392372218957027</v>
       </c>
       <c r="E33">
-        <v>-28.31656816056638</v>
+        <v>-25.14892776304501</v>
       </c>
       <c r="F33">
-        <v>-3.677756749337655</v>
+        <v>-3.247368524804338</v>
       </c>
       <c r="G33">
-        <v>-10.83857588567653</v>
+        <v>-8.068854111468976</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.087249762587389</v>
       </c>
       <c r="E34">
-        <v>-27.35267793955973</v>
+        <v>-25.39802553278493</v>
       </c>
       <c r="F34">
-        <v>-3.617570887319854</v>
+        <v>-3.27977591433666</v>
       </c>
       <c r="G34">
-        <v>-10.72717513251183</v>
+        <v>-6.813770458873575</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.829387544002972</v>
       </c>
       <c r="E35">
-        <v>-27.40368667078213</v>
+        <v>-23.74007421451869</v>
       </c>
       <c r="F35">
-        <v>-3.300446166138717</v>
+        <v>-3.504990787074984</v>
       </c>
       <c r="G35">
-        <v>-10.17473882709903</v>
+        <v>-7.236542731921789</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.625720202627459</v>
       </c>
       <c r="E36">
-        <v>-26.91557151444336</v>
+        <v>-25.11341094140285</v>
       </c>
       <c r="F36">
-        <v>-3.553055977255023</v>
+        <v>-3.75921591462675</v>
       </c>
       <c r="G36">
-        <v>-10.31934226122376</v>
+        <v>-8.344696564306815</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.491708622672992</v>
       </c>
       <c r="E37">
-        <v>-26.09646113593595</v>
+        <v>-24.91302596656344</v>
       </c>
       <c r="F37">
-        <v>-3.716345416429667</v>
+        <v>-3.232268215418706</v>
       </c>
       <c r="G37">
-        <v>-10.40351215666664</v>
+        <v>-6.50676296366413</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.430093016643237</v>
       </c>
       <c r="E38">
-        <v>-26.09056959125197</v>
+        <v>-24.07315253473086</v>
       </c>
       <c r="F38">
-        <v>-3.596831881023366</v>
+        <v>-3.764345165584885</v>
       </c>
       <c r="G38">
-        <v>-10.51417791620203</v>
+        <v>-6.790949562927637</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.438646724729565</v>
       </c>
       <c r="E39">
-        <v>-25.7110291277211</v>
+        <v>-23.66035042961365</v>
       </c>
       <c r="F39">
-        <v>-3.660981481063562</v>
+        <v>-3.300266410412309</v>
       </c>
       <c r="G39">
-        <v>-10.28884658805029</v>
+        <v>-6.221286844327762</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.517593878471001</v>
       </c>
       <c r="E40">
-        <v>-26.05101337079497</v>
+        <v>-23.86661336371502</v>
       </c>
       <c r="F40">
-        <v>-3.376945895787251</v>
+        <v>-3.649790237451741</v>
       </c>
       <c r="G40">
-        <v>-9.953187466183769</v>
+        <v>-6.563695438942055</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.651846047854362</v>
       </c>
       <c r="E41">
-        <v>-25.12598651372215</v>
+        <v>-22.06635474975773</v>
       </c>
       <c r="F41">
-        <v>-3.67784704138456</v>
+        <v>-4.016028861944861</v>
       </c>
       <c r="G41">
-        <v>-10.13553807312835</v>
+        <v>-5.618500194085292</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.837019217513665</v>
       </c>
       <c r="E42">
-        <v>-24.44422928034139</v>
+        <v>-22.59946935231072</v>
       </c>
       <c r="F42">
-        <v>-3.563078394461494</v>
+        <v>-3.861144866806423</v>
       </c>
       <c r="G42">
-        <v>-9.983768451117793</v>
+        <v>-6.659287266633358</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.052369323782634</v>
       </c>
       <c r="E43">
-        <v>-23.62264635502578</v>
+        <v>-21.31919729475819</v>
       </c>
       <c r="F43">
-        <v>-3.684996680438123</v>
+        <v>-3.389140292323862</v>
       </c>
       <c r="G43">
-        <v>-9.393801533508073</v>
+        <v>-7.455045838008331</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.289387226189392</v>
       </c>
       <c r="E44">
-        <v>-24.24097778145512</v>
+        <v>-21.27529373925382</v>
       </c>
       <c r="F44">
-        <v>-3.72382060387253</v>
+        <v>-4.034204899497087</v>
       </c>
       <c r="G44">
-        <v>-9.831726487717804</v>
+        <v>-6.342249077116691</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.531177769404851</v>
       </c>
       <c r="E45">
-        <v>-23.53573588187058</v>
+        <v>-21.22850554580657</v>
       </c>
       <c r="F45">
-        <v>-3.86564455853843</v>
+        <v>-3.65787096146605</v>
       </c>
       <c r="G45">
-        <v>-10.35507804522768</v>
+        <v>-7.194789187577855</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.766145875784265</v>
       </c>
       <c r="E46">
-        <v>-23.1910827820948</v>
+        <v>-19.73196262659572</v>
       </c>
       <c r="F46">
-        <v>-3.671314536046083</v>
+        <v>-3.551757925534836</v>
       </c>
       <c r="G46">
-        <v>-9.992699936202602</v>
+        <v>-6.458361664440761</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.987773678009059</v>
       </c>
       <c r="E47">
-        <v>-23.1949229280533</v>
+        <v>-20.33406853065557</v>
       </c>
       <c r="F47">
-        <v>-3.784785959616365</v>
+        <v>-4.52607620940099</v>
       </c>
       <c r="G47">
-        <v>-9.821928760141301</v>
+        <v>-7.681597780580192</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.1833597950244</v>
       </c>
       <c r="E48">
-        <v>-22.12871183684335</v>
+        <v>-19.25683060523694</v>
       </c>
       <c r="F48">
-        <v>-3.984192217553067</v>
+        <v>-3.78687344547142</v>
       </c>
       <c r="G48">
-        <v>-10.20399091730148</v>
+        <v>-6.808878157528443</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.356160659584081</v>
       </c>
       <c r="E49">
-        <v>-22.23169386425178</v>
+        <v>-18.83157066812463</v>
       </c>
       <c r="F49">
-        <v>-3.987981170053473</v>
+        <v>-4.205638846976057</v>
       </c>
       <c r="G49">
-        <v>-9.961111616249827</v>
+        <v>-6.862542536133161</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.498913544947339</v>
       </c>
       <c r="E50">
-        <v>-21.42036340408954</v>
+        <v>-19.22986807099527</v>
       </c>
       <c r="F50">
-        <v>-3.756030841962986</v>
+        <v>-4.191548317454437</v>
       </c>
       <c r="G50">
-        <v>-10.49787352627315</v>
+        <v>-7.459199864502589</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.62004069191296</v>
       </c>
       <c r="E51">
-        <v>-21.84023898560673</v>
+        <v>-19.26278554855702</v>
       </c>
       <c r="F51">
-        <v>-3.741999954894368</v>
+        <v>-4.485437332987049</v>
       </c>
       <c r="G51">
-        <v>-9.666441514103894</v>
+        <v>-7.062966111427163</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.718853562013815</v>
       </c>
       <c r="E52">
-        <v>-20.82962849826295</v>
+        <v>-19.15232248208792</v>
       </c>
       <c r="F52">
-        <v>-4.175050552260282</v>
+        <v>-4.367664197494029</v>
       </c>
       <c r="G52">
-        <v>-10.26302665559901</v>
+        <v>-6.602095574852237</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.804167967537316</v>
       </c>
       <c r="E53">
-        <v>-19.71486763721676</v>
+        <v>-18.51016675390423</v>
       </c>
       <c r="F53">
-        <v>-4.026752906341503</v>
+        <v>-3.952093809061989</v>
       </c>
       <c r="G53">
-        <v>-9.884875714537689</v>
+        <v>-7.051547460400296</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.884088357565317</v>
       </c>
       <c r="E54">
-        <v>-20.20944945443849</v>
+        <v>-18.30328341886381</v>
       </c>
       <c r="F54">
-        <v>-4.04142246467768</v>
+        <v>-4.300400764386708</v>
       </c>
       <c r="G54">
-        <v>-9.91051189858163</v>
+        <v>-6.771833166122312</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.960422397917158</v>
       </c>
       <c r="E55">
-        <v>-19.10477350500738</v>
+        <v>-17.66117750389421</v>
       </c>
       <c r="F55">
-        <v>-4.063157168592333</v>
+        <v>-4.397451460931296</v>
       </c>
       <c r="G55">
-        <v>-10.45557201792879</v>
+        <v>-7.214154957221697</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.046292401747431</v>
       </c>
       <c r="E56">
-        <v>-18.95400701987001</v>
+        <v>-15.76767761011899</v>
       </c>
       <c r="F56">
-        <v>-4.347568004302112</v>
+        <v>-4.297711883797222</v>
       </c>
       <c r="G56">
-        <v>-9.996785057044111</v>
+        <v>-6.91484520779071</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.137476174665418</v>
       </c>
       <c r="E57">
-        <v>-19.09714755477847</v>
+        <v>-16.3900665492592</v>
       </c>
       <c r="F57">
-        <v>-3.89703636963492</v>
+        <v>-4.257072179015878</v>
       </c>
       <c r="G57">
-        <v>-10.12605862404311</v>
+        <v>-7.824383417960988</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.243654602629125</v>
       </c>
       <c r="E58">
-        <v>-18.46955087052944</v>
+        <v>-15.13748158178956</v>
       </c>
       <c r="F58">
-        <v>-3.878817256977748</v>
+        <v>-3.988599132135961</v>
       </c>
       <c r="G58">
-        <v>-10.67767134284448</v>
+        <v>-7.162190251384771</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.357453890513035</v>
       </c>
       <c r="E59">
-        <v>-18.9260165220286</v>
+        <v>-16.45642227889359</v>
       </c>
       <c r="F59">
-        <v>-4.109853067455544</v>
+        <v>-3.782813616830299</v>
       </c>
       <c r="G59">
-        <v>-10.53682818862688</v>
+        <v>-7.464869815357309</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.483780576306591</v>
       </c>
       <c r="E60">
-        <v>-18.23632993066041</v>
+        <v>-16.24264207793949</v>
       </c>
       <c r="F60">
-        <v>-3.920055871391316</v>
+        <v>-3.722843130337226</v>
       </c>
       <c r="G60">
-        <v>-10.7569751867147</v>
+        <v>-8.274212643988383</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.618792587890962</v>
       </c>
       <c r="E61">
-        <v>-17.27478093071573</v>
+        <v>-15.72568054217185</v>
       </c>
       <c r="F61">
-        <v>-4.141744384095922</v>
+        <v>-4.32941101920015</v>
       </c>
       <c r="G61">
-        <v>-11.22339755016821</v>
+        <v>-7.730291108522351</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.75865593087493</v>
       </c>
       <c r="E62">
-        <v>-17.07376649798925</v>
+        <v>-16.00352506491247</v>
       </c>
       <c r="F62">
-        <v>-3.906497153742293</v>
+        <v>-4.000405852728062</v>
       </c>
       <c r="G62">
-        <v>-11.37973135136795</v>
+        <v>-7.691690818097044</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.905803554473168</v>
       </c>
       <c r="E63">
-        <v>-17.54024460551937</v>
+        <v>-15.61216075574757</v>
       </c>
       <c r="F63">
-        <v>-4.029262859571986</v>
+        <v>-3.987888392904359</v>
       </c>
       <c r="G63">
-        <v>-11.51850405478155</v>
+        <v>-7.370095011834308</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.047653941855479</v>
       </c>
       <c r="E64">
-        <v>-17.16785007397261</v>
+        <v>-15.44853340442842</v>
       </c>
       <c r="F64">
-        <v>-3.741756414877945</v>
+        <v>-3.72377918550239</v>
       </c>
       <c r="G64">
-        <v>-11.47278023235069</v>
+        <v>-7.51609624634336</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.188268352946707</v>
       </c>
       <c r="E65">
-        <v>-17.50689239445288</v>
+        <v>-15.89003244933224</v>
       </c>
       <c r="F65">
-        <v>-4.008192506314377</v>
+        <v>-3.927002560431192</v>
       </c>
       <c r="G65">
-        <v>-11.94421958356858</v>
+        <v>-7.969984343439788</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.31490883857324</v>
       </c>
       <c r="E66">
-        <v>-16.84895493435246</v>
+        <v>-15.26654309100816</v>
       </c>
       <c r="F66">
-        <v>-4.137262916446777</v>
+        <v>-4.017695537159294</v>
       </c>
       <c r="G66">
-        <v>-11.58110648091419</v>
+        <v>-9.35115549689997</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.43292376653042</v>
       </c>
       <c r="E67">
-        <v>-16.8154396982217</v>
+        <v>-14.80949779483602</v>
       </c>
       <c r="F67">
-        <v>-4.208485945739478</v>
+        <v>-3.690778684909663</v>
       </c>
       <c r="G67">
-        <v>-11.96888124480937</v>
+        <v>-9.053660262991356</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.535934618944388</v>
       </c>
       <c r="E68">
-        <v>-16.82623105178197</v>
+        <v>-14.27116186175218</v>
       </c>
       <c r="F68">
-        <v>-4.092360433010627</v>
+        <v>-4.264674106671369</v>
       </c>
       <c r="G68">
-        <v>-12.05492143654113</v>
+        <v>-8.822895231937169</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.626145748469959</v>
       </c>
       <c r="E69">
-        <v>-16.99041087693006</v>
+        <v>-13.89294824110556</v>
       </c>
       <c r="F69">
-        <v>-4.243032179905829</v>
+        <v>-3.868467634647171</v>
       </c>
       <c r="G69">
-        <v>-11.80236909433223</v>
+        <v>-8.690688252864023</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.708310281261806</v>
       </c>
       <c r="E70">
-        <v>-16.18230016178728</v>
+        <v>-13.29453757183597</v>
       </c>
       <c r="F70">
-        <v>-4.098931871617036</v>
+        <v>-4.650259251856872</v>
       </c>
       <c r="G70">
-        <v>-11.5194949836925</v>
+        <v>-9.446977010100435</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.77850181495465</v>
       </c>
       <c r="E71">
-        <v>-17.1138842492232</v>
+        <v>-14.58551947041664</v>
       </c>
       <c r="F71">
-        <v>-4.114276549386494</v>
+        <v>-4.196849868832354</v>
       </c>
       <c r="G71">
-        <v>-11.81897207542302</v>
+        <v>-9.320334982792106</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.848391518512747</v>
       </c>
       <c r="E72">
-        <v>-17.13961956700879</v>
+        <v>-14.4572051594093</v>
       </c>
       <c r="F72">
-        <v>-4.512054434373802</v>
+        <v>-4.305833197814268</v>
       </c>
       <c r="G72">
-        <v>-11.73434280896182</v>
+        <v>-9.125525577586314</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.909093547001724</v>
       </c>
       <c r="E73">
-        <v>-17.35983472952779</v>
+        <v>-15.01035825944624</v>
       </c>
       <c r="F73">
-        <v>-4.224707036221099</v>
+        <v>-4.029141089563774</v>
       </c>
       <c r="G73">
-        <v>-11.44743279580398</v>
+        <v>-8.59905029715185</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.967919696559184</v>
       </c>
       <c r="E74">
-        <v>-17.25685270211936</v>
+        <v>-14.37940597595753</v>
       </c>
       <c r="F74">
-        <v>-4.140100074801365</v>
+        <v>-4.196836614953909</v>
       </c>
       <c r="G74">
-        <v>-11.51217457839338</v>
+        <v>-9.321115913523254</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.01385716713641</v>
       </c>
       <c r="E75">
-        <v>-17.87844915830823</v>
+        <v>-14.40667191795771</v>
       </c>
       <c r="F75">
-        <v>-4.595042765888465</v>
+        <v>-4.43692233930729</v>
       </c>
       <c r="G75">
-        <v>-11.68623353845724</v>
+        <v>-8.656875264693944</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.0508165243556</v>
       </c>
       <c r="E76">
-        <v>-17.83501203562665</v>
+        <v>-14.99152433604834</v>
       </c>
       <c r="F76">
-        <v>-4.516563238147239</v>
+        <v>-4.613886467567348</v>
       </c>
       <c r="G76">
-        <v>-10.84507270436423</v>
+        <v>-8.090057365186107</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.07584781151274</v>
       </c>
       <c r="E77">
-        <v>-18.2652532941474</v>
+        <v>-15.77241892240502</v>
       </c>
       <c r="F77">
-        <v>-4.339421010895579</v>
+        <v>-4.248626144976934</v>
       </c>
       <c r="G77">
-        <v>-11.16296401148636</v>
+        <v>-6.96566476730339</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.08444264185748</v>
       </c>
       <c r="E78">
-        <v>-17.8428327102379</v>
+        <v>-16.61498226779816</v>
       </c>
       <c r="F78">
-        <v>-4.536267613557632</v>
+        <v>-4.53602738701082</v>
       </c>
       <c r="G78">
-        <v>-11.15497751821067</v>
+        <v>-7.221767391239609</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.08320601955664</v>
       </c>
       <c r="E79">
-        <v>-18.41553523256595</v>
+        <v>-16.20039594392193</v>
       </c>
       <c r="F79">
-        <v>-4.625761942653882</v>
+        <v>-4.705109599433241</v>
       </c>
       <c r="G79">
-        <v>-10.97123239210332</v>
+        <v>-7.929280789994876</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.06361097587833</v>
       </c>
       <c r="E80">
-        <v>-19.1752139181967</v>
+        <v>-16.12064045969884</v>
       </c>
       <c r="F80">
-        <v>-4.882441522820142</v>
+        <v>-4.577653677368898</v>
       </c>
       <c r="G80">
-        <v>-10.57967109852855</v>
+        <v>-7.728050034197251</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.03491687982538</v>
       </c>
       <c r="E81">
-        <v>-19.73497406181082</v>
+        <v>-16.89246451261816</v>
       </c>
       <c r="F81">
-        <v>-4.619675927345514</v>
+        <v>-5.628417847002403</v>
       </c>
       <c r="G81">
-        <v>-10.54756106434782</v>
+        <v>-7.933316692512993</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.986404101761988</v>
       </c>
       <c r="E82">
-        <v>-20.30234204175783</v>
+        <v>-18.31490348316749</v>
       </c>
       <c r="F82">
-        <v>-4.721038276221672</v>
+        <v>-5.217166566208561</v>
       </c>
       <c r="G82">
-        <v>-10.32593751655825</v>
+        <v>-7.36039243968303</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.924398224375258</v>
       </c>
       <c r="E83">
-        <v>-20.79547927577111</v>
+        <v>-18.06265842399224</v>
       </c>
       <c r="F83">
-        <v>-5.025918070454628</v>
+        <v>-4.937184182634147</v>
       </c>
       <c r="G83">
-        <v>-10.30444879656544</v>
+        <v>-7.862619492793197</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.84364802252799</v>
       </c>
       <c r="E84">
-        <v>-21.89008389900916</v>
+        <v>-19.1166516923295</v>
       </c>
       <c r="F84">
-        <v>-5.103131852804375</v>
+        <v>-4.971276471463764</v>
       </c>
       <c r="G84">
-        <v>-9.809873552131901</v>
+        <v>-7.262651411870291</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.746650788059071</v>
       </c>
       <c r="E85">
-        <v>-23.30887744798232</v>
+        <v>-20.1161764753025</v>
       </c>
       <c r="F85">
-        <v>-4.996162284978666</v>
+        <v>-5.128172571023602</v>
       </c>
       <c r="G85">
-        <v>-10.39381942818004</v>
+        <v>-6.639990402642264</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.642769479846462</v>
       </c>
       <c r="E86">
-        <v>-23.54621477072432</v>
+        <v>-21.4352167988347</v>
       </c>
       <c r="F86">
-        <v>-5.176318112841711</v>
+        <v>-5.232812769712638</v>
       </c>
       <c r="G86">
-        <v>-10.07078316565271</v>
+        <v>-6.768017105448678</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.531636202146231</v>
       </c>
       <c r="E87">
-        <v>-24.61333608520982</v>
+        <v>-23.32455955347088</v>
       </c>
       <c r="F87">
-        <v>-5.327711367744752</v>
+        <v>-4.829031706157242</v>
       </c>
       <c r="G87">
-        <v>-10.09782043130253</v>
+        <v>-7.865080408962781</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.43281386997344</v>
       </c>
       <c r="E88">
-        <v>-25.73010306024141</v>
+        <v>-23.85724847946716</v>
       </c>
       <c r="F88">
-        <v>-5.362095241900154</v>
+        <v>-5.662890356469905</v>
       </c>
       <c r="G88">
-        <v>-9.80356376307309</v>
+        <v>-7.446465443630383</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.347353106938707</v>
       </c>
       <c r="E89">
-        <v>-27.79282749920926</v>
+        <v>-25.36701454278041</v>
       </c>
       <c r="F89">
-        <v>-5.410493435776118</v>
+        <v>-6.002995646139507</v>
       </c>
       <c r="G89">
-        <v>-10.14237942007979</v>
+        <v>-7.771808404914005</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.298014883007395</v>
       </c>
       <c r="E90">
-        <v>-28.48891735282431</v>
+        <v>-27.06837128441017</v>
       </c>
       <c r="F90">
-        <v>-5.464737418413637</v>
+        <v>-6.074284116457028</v>
       </c>
       <c r="G90">
-        <v>-10.07523250208731</v>
+        <v>-6.557224870026831</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.290433547495901</v>
       </c>
       <c r="E91">
-        <v>-29.70444808172618</v>
+        <v>-28.61600444737557</v>
       </c>
       <c r="F91">
-        <v>-5.497105874678028</v>
+        <v>-5.807767673382524</v>
       </c>
       <c r="G91">
-        <v>-10.33345151392938</v>
+        <v>-7.107771191821381</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.341539876888932</v>
       </c>
       <c r="E92">
-        <v>-31.58955444892818</v>
+        <v>-31.27244126383005</v>
       </c>
       <c r="F92">
-        <v>-5.792292941930826</v>
+        <v>-5.912693658825527</v>
       </c>
       <c r="G92">
-        <v>-10.57493629581827</v>
+        <v>-8.729738070642973</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.464275332677079</v>
       </c>
       <c r="E93">
-        <v>-33.48374946346358</v>
+        <v>-33.14644834123926</v>
       </c>
       <c r="F93">
-        <v>-5.479972751685926</v>
+        <v>-6.225365076849214</v>
       </c>
       <c r="G93">
-        <v>-10.78187637712933</v>
+        <v>-7.636943636377708</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.657511045773989</v>
       </c>
       <c r="E94">
-        <v>-35.23052453515328</v>
+        <v>-34.88640805954741</v>
       </c>
       <c r="F94">
-        <v>-5.614396900342619</v>
+        <v>-6.140921303807833</v>
       </c>
       <c r="G94">
-        <v>-10.73450866269718</v>
+        <v>-8.083973980414898</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.933919176752923</v>
       </c>
       <c r="E95">
-        <v>-36.63422241602187</v>
+        <v>-37.23321046572744</v>
       </c>
       <c r="F95">
-        <v>-5.700774082902135</v>
+        <v>-6.729318125322946</v>
       </c>
       <c r="G95">
-        <v>-10.72057659595578</v>
+        <v>-8.823613819458688</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.28553538783333</v>
       </c>
       <c r="E96">
-        <v>-39.04530424650378</v>
+        <v>-39.14572995033488</v>
       </c>
       <c r="F96">
-        <v>-5.721339960411438</v>
+        <v>-6.129008552188172</v>
       </c>
       <c r="G96">
-        <v>-11.19593700693722</v>
+        <v>-9.263635474244902</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.71228534178518</v>
       </c>
       <c r="E97">
-        <v>-41.84608617195276</v>
+        <v>-41.54936244107417</v>
       </c>
       <c r="F97">
-        <v>-5.775297327927589</v>
+        <v>-6.055833060927073</v>
       </c>
       <c r="G97">
-        <v>-11.59827383211321</v>
+        <v>-8.71558616205709</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.21254896164899</v>
       </c>
       <c r="E98">
-        <v>-43.49780178151045</v>
+        <v>-44.08838045498377</v>
       </c>
       <c r="F98">
-        <v>-5.637001390030212</v>
+        <v>-5.881362318549441</v>
       </c>
       <c r="G98">
-        <v>-11.35754044996143</v>
+        <v>-9.669709610777101</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.76185092241375</v>
       </c>
       <c r="E99">
-        <v>-45.61870805452885</v>
+        <v>-45.86776959647671</v>
       </c>
       <c r="F99">
-        <v>-5.825254509255622</v>
+        <v>-6.32530926073178</v>
       </c>
       <c r="G99">
-        <v>-12.16292940661337</v>
+        <v>-9.596863210935869</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.38264032798785</v>
       </c>
       <c r="E100">
-        <v>-47.74026189933035</v>
+        <v>-47.44953613227491</v>
       </c>
       <c r="F100">
-        <v>-5.831253545986696</v>
+        <v>-5.936394906954426</v>
       </c>
       <c r="G100">
-        <v>-12.48986376035332</v>
+        <v>-9.480005786317806</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.99954020750034</v>
       </c>
       <c r="E101">
-        <v>-49.15043436591141</v>
+        <v>-51.67062864548963</v>
       </c>
       <c r="F101">
-        <v>-6.128267163362668</v>
+        <v>-5.931336067225529</v>
       </c>
       <c r="G101">
-        <v>-12.63466406777162</v>
+        <v>-10.17038136486809</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.70451488430509</v>
       </c>
       <c r="E102">
-        <v>-51.76078150603433</v>
+        <v>-51.85115512968691</v>
       </c>
       <c r="F102">
-        <v>-5.953861862009856</v>
+        <v>-6.89054203037871</v>
       </c>
       <c r="G102">
-        <v>-12.83069736861908</v>
+        <v>-11.27631052903581</v>
       </c>
     </row>
   </sheetData>
